--- a/admin_testy/reporty_google_testy/google_data/Pobočky/Chodov/Databaze Chodov 2026.xlsx
+++ b/admin_testy/reporty_google_testy/google_data/Pobočky/Chodov/Databaze Chodov 2026.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5674" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5738" uniqueCount="371">
   <si>
     <t>Datum</t>
   </si>
@@ -447,6 +447,18 @@
     <t>11 min 39 s</t>
   </si>
   <si>
+    <t>20.05.2026</t>
+  </si>
+  <si>
+    <t>10 min 53 s</t>
+  </si>
+  <si>
+    <t>21.05.2026</t>
+  </si>
+  <si>
+    <t>14 min 14 s</t>
+  </si>
+  <si>
     <t>01.04.2026</t>
   </si>
   <si>
@@ -898,9 +910,6 @@
   </si>
   <si>
     <t>15.02.2026</t>
-  </si>
-  <si>
-    <t>10 min 53 s</t>
   </si>
   <si>
     <t>16.02.2026</t>
@@ -5552,6 +5561,412 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="L116" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M116" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="L117" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M117" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="N117" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O117" s="3">
+        <v>270.0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L118" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M118" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="N118" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O118" s="3">
+        <v>585.0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="P119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S119" s="3">
+        <v>13370.3</v>
+      </c>
+      <c r="T119" s="3">
+        <v>6257.0</v>
+      </c>
+      <c r="U119" s="3">
+        <v>8325.0</v>
+      </c>
+      <c r="V119" s="3">
+        <v>11969.0</v>
+      </c>
+      <c r="W119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X119" s="3">
+        <v>793.0</v>
+      </c>
+      <c r="Y119" s="3">
+        <v>4541.0</v>
+      </c>
+      <c r="AA119" s="3">
+        <v>4250.0</v>
+      </c>
+      <c r="AB119" s="3">
+        <v>50723.8</v>
+      </c>
+      <c r="AC119" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AD119" s="3">
+        <v>0.3123841311878918</v>
+      </c>
+      <c r="AE119" s="3">
+        <v>1098.0</v>
+      </c>
+      <c r="AG119" s="3">
+        <v>59.0</v>
+      </c>
+      <c r="AI119" s="3">
+        <v>855.0</v>
+      </c>
+      <c r="AJ119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AM119" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN119" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AO119" s="3">
+        <v>140.0</v>
+      </c>
+      <c r="AP119" s="3">
+        <v>28.0</v>
+      </c>
+      <c r="AQ119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AR119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AT119" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AU119" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AV119" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L122" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M122" s="3">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L123" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M123" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="N123" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="O123" s="3">
+        <v>765.0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="P124" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q124" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="S124" s="3">
+        <v>12452.0</v>
+      </c>
+      <c r="T124" s="3">
+        <v>3722.0</v>
+      </c>
+      <c r="U124" s="3">
+        <v>12420.0</v>
+      </c>
+      <c r="V124" s="3">
+        <v>12721.5</v>
+      </c>
+      <c r="W124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X124" s="3">
+        <v>439.0</v>
+      </c>
+      <c r="Y124" s="3">
+        <v>5790.0</v>
+      </c>
+      <c r="AA124" s="3">
+        <v>3487.0</v>
+      </c>
+      <c r="AB124" s="3">
+        <v>52357.5</v>
+      </c>
+      <c r="AC124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD124" s="3">
+        <v>0.27294625972493697</v>
+      </c>
+      <c r="AE124" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="AI124" s="3">
+        <v>765.0</v>
+      </c>
+      <c r="AJ124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AK124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AL124" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="AM124" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN124" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AO124" s="3">
+        <v>129.0</v>
+      </c>
+      <c r="AP124" s="3">
+        <v>27.0</v>
+      </c>
+      <c r="AQ124" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AR124" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AS124" s="3">
+        <v>0.14814814814814814</v>
+      </c>
+      <c r="AT124" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AU124" s="3">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="AV124" s="3">
+        <v>0.037037037037037035</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -5712,7 +6127,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>96</v>
@@ -5732,7 +6147,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>96</v>
@@ -5752,7 +6167,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>96</v>
@@ -5775,7 +6190,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>96</v>
@@ -5804,7 +6219,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>96</v>
@@ -5833,7 +6248,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>96</v>
@@ -5896,7 +6311,7 @@
         <v>5.0</v>
       </c>
       <c r="AM7" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AN7" s="3">
         <v>2.0</v>
@@ -5928,7 +6343,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>103</v>
@@ -5948,7 +6363,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>103</v>
@@ -5968,7 +6383,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>103</v>
@@ -5988,7 +6403,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>103</v>
@@ -6008,7 +6423,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>103</v>
@@ -6031,7 +6446,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>103</v>
@@ -6046,7 +6461,7 @@
         <v>104</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>107</v>
@@ -6063,7 +6478,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>103</v>
@@ -6126,7 +6541,7 @@
         <v>15.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -6158,7 +6573,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -6178,7 +6593,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -6198,7 +6613,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>49</v>
@@ -6218,7 +6633,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>49</v>
@@ -6238,7 +6653,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>49</v>
@@ -6267,13 +6682,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>55</v>
@@ -6296,7 +6711,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>49</v>
@@ -6325,7 +6740,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>49</v>
@@ -6420,7 +6835,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>64</v>
@@ -6443,7 +6858,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>64</v>
@@ -6463,7 +6878,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>64</v>
@@ -6483,7 +6898,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>64</v>
@@ -6503,7 +6918,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>64</v>
@@ -6532,7 +6947,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>64</v>
@@ -6561,7 +6976,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>64</v>
@@ -6656,7 +7071,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>76</v>
@@ -6676,7 +7091,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>76</v>
@@ -6696,7 +7111,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>76</v>
@@ -6725,7 +7140,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>76</v>
@@ -6754,7 +7169,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>76</v>
@@ -6817,7 +7232,7 @@
         <v>3.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="AN34" s="3">
         <v>2.0</v>
@@ -6849,7 +7264,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>85</v>
@@ -6869,7 +7284,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>85</v>
@@ -6889,7 +7304,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>85</v>
@@ -6909,7 +7324,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>85</v>
@@ -6938,7 +7353,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>85</v>
@@ -6998,7 +7413,7 @@
         <v>2.0</v>
       </c>
       <c r="AM39" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN39" s="3">
         <v>1.0</v>
@@ -7030,7 +7445,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>92</v>
@@ -7050,7 +7465,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>92</v>
@@ -7070,7 +7485,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>92</v>
@@ -7090,7 +7505,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>92</v>
@@ -7110,7 +7525,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>92</v>
@@ -7133,7 +7548,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>92</v>
@@ -7162,7 +7577,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>92</v>
@@ -7185,7 +7600,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>92</v>
@@ -7251,7 +7666,7 @@
         <v>1.0</v>
       </c>
       <c r="AM47" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AN47" s="3">
         <v>1.0</v>
@@ -7283,7 +7698,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>96</v>
@@ -7303,7 +7718,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>96</v>
@@ -7323,7 +7738,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>96</v>
@@ -7343,7 +7758,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>96</v>
@@ -7366,7 +7781,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>96</v>
@@ -7395,7 +7810,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>96</v>
@@ -7424,7 +7839,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>96</v>
@@ -7490,7 +7905,7 @@
         <v>1.0</v>
       </c>
       <c r="AM54" s="1" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="AN54" s="3">
         <v>2.0</v>
@@ -7522,7 +7937,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>103</v>
@@ -7542,7 +7957,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>103</v>
@@ -7562,7 +7977,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>103</v>
@@ -7585,7 +8000,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>103</v>
@@ -7614,7 +8029,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>103</v>
@@ -7643,7 +8058,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>103</v>
@@ -7706,7 +8121,7 @@
         <v>1.0</v>
       </c>
       <c r="AM60" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AN60" s="3">
         <v>2.0</v>
@@ -7738,7 +8153,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
@@ -7758,7 +8173,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
@@ -7778,7 +8193,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
@@ -7798,7 +8213,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -7818,7 +8233,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -7838,7 +8253,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -7867,7 +8282,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>49</v>
@@ -7896,7 +8311,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>49</v>
@@ -7905,7 +8320,7 @@
         <v>88</v>
       </c>
       <c r="I68" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>72</v>
@@ -7925,7 +8340,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>49</v>
@@ -7988,7 +8403,7 @@
         <v>7.0</v>
       </c>
       <c r="AM69" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AN69" s="3">
         <v>3.0</v>
@@ -8020,7 +8435,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>64</v>
@@ -8040,7 +8455,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>64</v>
@@ -8060,7 +8475,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>64</v>
@@ -8080,7 +8495,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>64</v>
@@ -8109,7 +8524,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>64</v>
@@ -8138,7 +8553,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>64</v>
@@ -8167,7 +8582,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>64</v>
@@ -8230,7 +8645,7 @@
         <v>5.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN76" s="3">
         <v>3.0</v>
@@ -8262,7 +8677,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>76</v>
@@ -8282,7 +8697,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>76</v>
@@ -8302,7 +8717,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>76</v>
@@ -8322,7 +8737,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>76</v>
@@ -8351,7 +8766,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>76</v>
@@ -8380,7 +8795,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>76</v>
@@ -8440,7 +8855,7 @@
         <v>4.0</v>
       </c>
       <c r="AM82" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN82" s="3">
         <v>2.0</v>
@@ -8472,7 +8887,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>85</v>
@@ -8492,7 +8907,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>85</v>
@@ -8512,7 +8927,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>85</v>
@@ -8535,7 +8950,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>85</v>
@@ -8564,7 +8979,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>85</v>
@@ -8593,7 +9008,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>85</v>
@@ -8659,7 +9074,7 @@
         <v>2.0</v>
       </c>
       <c r="AM88" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AN88" s="3">
         <v>2.0</v>
@@ -8691,7 +9106,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>92</v>
@@ -8711,7 +9126,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>92</v>
@@ -8731,7 +9146,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>92</v>
@@ -8754,7 +9169,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>92</v>
@@ -8783,7 +9198,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>92</v>
@@ -8812,7 +9227,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>92</v>
@@ -8872,7 +9287,7 @@
         <v>1.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AN94" s="3">
         <v>2.0</v>
@@ -8904,7 +9319,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>96</v>
@@ -8924,7 +9339,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>96</v>
@@ -8944,7 +9359,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>96</v>
@@ -8967,7 +9382,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>96</v>
@@ -8976,7 +9391,7 @@
         <v>98</v>
       </c>
       <c r="I98" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>100</v>
@@ -8996,7 +9411,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>96</v>
@@ -9025,7 +9440,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>96</v>
@@ -9094,7 +9509,7 @@
         <v>1.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AN100" s="3">
         <v>2.0</v>
@@ -9126,7 +9541,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>103</v>
@@ -9146,7 +9561,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>103</v>
@@ -9166,7 +9581,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>103</v>
@@ -9186,7 +9601,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>103</v>
@@ -9209,13 +9624,13 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>55</v>
@@ -9232,7 +9647,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>103</v>
@@ -9261,7 +9676,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>103</v>
@@ -9324,7 +9739,7 @@
         <v>9.0</v>
       </c>
       <c r="AM107" s="1" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="AN107" s="3">
         <v>1.0</v>
@@ -9356,7 +9771,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>49</v>
@@ -9376,7 +9791,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>49</v>
@@ -9396,7 +9811,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>49</v>
@@ -9416,7 +9831,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>49</v>
@@ -9449,7 +9864,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>49</v>
@@ -9482,7 +9897,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>49</v>
@@ -9492,7 +9907,7 @@
       <c r="E113" s="1"/>
       <c r="G113" s="1"/>
       <c r="H113" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>55</v>
@@ -9515,7 +9930,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -9548,7 +9963,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -9618,7 +10033,7 @@
         <v>2.0</v>
       </c>
       <c r="AM115" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AN115" s="3">
         <v>4.0</v>
@@ -9650,7 +10065,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>64</v>
@@ -9662,7 +10077,7 @@
         <v>51</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G116" s="2" t="s">
         <v>105</v>
@@ -9670,7 +10085,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>64</v>
@@ -9690,7 +10105,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>64</v>
@@ -9710,7 +10125,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>64</v>
@@ -9730,7 +10145,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>64</v>
@@ -9753,7 +10168,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>64</v>
@@ -9782,7 +10197,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>64</v>
@@ -9811,7 +10226,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>64</v>
@@ -9877,7 +10292,7 @@
         <v>3.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="AN123" s="3">
         <v>2.0</v>
@@ -9909,7 +10324,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>76</v>
@@ -9929,7 +10344,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>76</v>
@@ -9949,7 +10364,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>76</v>
@@ -9978,7 +10393,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>76</v>
@@ -10038,7 +10453,7 @@
         <v>12.0</v>
       </c>
       <c r="AM127" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AN127" s="3">
         <v>1.0</v>
@@ -10070,7 +10485,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>85</v>
@@ -10090,7 +10505,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>85</v>
@@ -10110,7 +10525,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>85</v>
@@ -10133,7 +10548,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>85</v>
@@ -10162,7 +10577,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>85</v>
@@ -10228,7 +10643,7 @@
         <v>0.0</v>
       </c>
       <c r="AM132" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="AN132" s="3">
         <v>1.0</v>
@@ -10260,7 +10675,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>92</v>
@@ -10280,7 +10695,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>92</v>
@@ -10300,7 +10715,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>92</v>
@@ -10323,7 +10738,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>92</v>
@@ -10352,7 +10767,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>92</v>
@@ -10381,7 +10796,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>92</v>
@@ -10444,7 +10859,7 @@
         <v>1.0</v>
       </c>
       <c r="AM138" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AN138" s="3">
         <v>2.0</v>
@@ -10476,7 +10891,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>96</v>
@@ -10496,7 +10911,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>96</v>
@@ -10516,7 +10931,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>96</v>
@@ -10536,7 +10951,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>96</v>
@@ -10559,7 +10974,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>96</v>
@@ -10568,7 +10983,7 @@
         <v>98</v>
       </c>
       <c r="I143" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>52</v>
@@ -10588,7 +11003,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>96</v>
@@ -10617,7 +11032,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>96</v>
@@ -10680,7 +11095,7 @@
         <v>1.0</v>
       </c>
       <c r="AM145" s="1" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AN145" s="3">
         <v>2.0</v>
@@ -10712,7 +11127,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>103</v>
@@ -10732,7 +11147,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>103</v>
@@ -10752,7 +11167,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>103</v>
@@ -10775,7 +11190,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>103</v>
@@ -10804,7 +11219,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>103</v>
@@ -10864,7 +11279,7 @@
         <v>5.0</v>
       </c>
       <c r="AM150" s="1" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AN150" s="3">
         <v>1.0</v>
@@ -10896,7 +11311,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>49</v>
@@ -10916,7 +11331,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>49</v>
@@ -10936,7 +11351,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>49</v>
@@ -10956,7 +11371,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>49</v>
@@ -10976,7 +11391,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>49</v>
@@ -11005,7 +11420,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>49</v>
@@ -11034,7 +11449,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>49</v>
@@ -11063,13 +11478,13 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H158" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I158" s="2" t="s">
         <v>55</v>
@@ -11092,7 +11507,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>49</v>
@@ -11152,7 +11567,7 @@
         <v>2.0</v>
       </c>
       <c r="AM159" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="AN159" s="3">
         <v>4.0</v>
@@ -11184,7 +11599,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>64</v>
@@ -11204,7 +11619,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>64</v>
@@ -11224,7 +11639,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>64</v>
@@ -11244,7 +11659,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>64</v>
@@ -11267,7 +11682,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>64</v>
@@ -11296,7 +11711,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>64</v>
@@ -11325,7 +11740,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>64</v>
@@ -11388,7 +11803,7 @@
         <v>3.0</v>
       </c>
       <c r="AM166" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AN166" s="3">
         <v>2.0</v>
@@ -11420,7 +11835,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>76</v>
@@ -11440,7 +11855,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>76</v>
@@ -11460,7 +11875,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>76</v>
@@ -11480,7 +11895,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>76</v>
@@ -11500,7 +11915,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>76</v>
@@ -11529,7 +11944,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>76</v>
@@ -11558,7 +11973,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>76</v>
@@ -11618,7 +12033,7 @@
         <v>4.0</v>
       </c>
       <c r="AM173" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AN173" s="3">
         <v>2.0</v>
@@ -11650,7 +12065,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>85</v>
@@ -11670,7 +12085,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>85</v>
@@ -11690,7 +12105,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>85</v>
@@ -11710,7 +12125,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>85</v>
@@ -11737,7 +12152,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>85</v>
@@ -11770,7 +12185,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>85</v>
@@ -11840,7 +12255,7 @@
         <v>0.0</v>
       </c>
       <c r="AM179" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AN179" s="3">
         <v>1.0</v>
@@ -11872,7 +12287,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>92</v>
@@ -11892,7 +12307,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>92</v>
@@ -11912,7 +12327,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>92</v>
@@ -11941,7 +12356,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>92</v>
@@ -11970,7 +12385,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>92</v>
@@ -12033,7 +12448,7 @@
         <v>0.0</v>
       </c>
       <c r="AM184" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="AN184" s="3">
         <v>2.0</v>
@@ -12065,7 +12480,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>96</v>
@@ -12085,7 +12500,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>96</v>
@@ -12105,7 +12520,7 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>96</v>
@@ -12125,7 +12540,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>96</v>
@@ -12148,7 +12563,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>96</v>
@@ -12177,7 +12592,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>96</v>
@@ -12206,7 +12621,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>96</v>
@@ -12272,7 +12687,7 @@
         <v>0.0</v>
       </c>
       <c r="AM191" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AN191" s="3">
         <v>2.0</v>
@@ -12304,7 +12719,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>103</v>
@@ -12324,7 +12739,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>103</v>
@@ -12344,7 +12759,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>103</v>
@@ -12367,7 +12782,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>103</v>
@@ -12396,7 +12811,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>103</v>
@@ -12459,7 +12874,7 @@
         <v>1.0</v>
       </c>
       <c r="AM196" s="1" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AN196" s="3">
         <v>1.0</v>
@@ -12649,7 +13064,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>76</v>
@@ -12669,7 +13084,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>76</v>
@@ -12689,7 +13104,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>76</v>
@@ -12709,13 +13124,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>60</v>
@@ -12738,7 +13153,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -12767,7 +13182,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -12796,7 +13211,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>76</v>
@@ -12856,7 +13271,7 @@
         <v>11.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN8" s="3">
         <v>3.0</v>
@@ -12888,7 +13303,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>85</v>
@@ -12908,7 +13323,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>85</v>
@@ -12931,7 +13346,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>85</v>
@@ -12954,7 +13369,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>85</v>
@@ -12983,7 +13398,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>85</v>
@@ -13075,7 +13490,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>92</v>
@@ -13095,7 +13510,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>92</v>
@@ -13118,13 +13533,13 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>55</v>
@@ -13138,13 +13553,13 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>55</v>
@@ -13167,7 +13582,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>92</v>
@@ -13196,7 +13611,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>92</v>
@@ -13262,7 +13677,7 @@
         <v>1.0</v>
       </c>
       <c r="AM19" s="1" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AN19" s="3">
         <v>2.0</v>
@@ -13294,7 +13709,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>96</v>
@@ -13314,7 +13729,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>96</v>
@@ -13334,7 +13749,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>96</v>
@@ -13357,13 +13772,13 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>96</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>55</v>
@@ -13377,7 +13792,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>96</v>
@@ -13400,7 +13815,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>96</v>
@@ -13429,7 +13844,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>96</v>
@@ -13492,7 +13907,7 @@
         <v>0.0</v>
       </c>
       <c r="AM26" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AN26" s="3">
         <v>1.0</v>
@@ -13524,7 +13939,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>103</v>
@@ -13544,7 +13959,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>103</v>
@@ -13564,7 +13979,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>103</v>
@@ -13587,13 +14002,13 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>55</v>
@@ -13607,13 +14022,13 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>55</v>
@@ -13636,7 +14051,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>103</v>
@@ -13665,7 +14080,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>103</v>
@@ -13728,7 +14143,7 @@
         <v>1.0</v>
       </c>
       <c r="AM33" s="1" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="AN33" s="3">
         <v>2.0</v>
@@ -13760,7 +14175,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>49</v>
@@ -13780,7 +14195,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -13800,7 +14215,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -13820,7 +14235,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
@@ -13849,7 +14264,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>49</v>
@@ -13878,7 +14293,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>49</v>
@@ -13901,13 +14316,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>55</v>
@@ -13930,13 +14345,13 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>55</v>
@@ -13950,7 +14365,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>49</v>
@@ -14010,7 +14425,7 @@
         <v>10.0</v>
       </c>
       <c r="AM42" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="AN42" s="3">
         <v>3.0</v>
@@ -14042,7 +14457,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>64</v>
@@ -14062,7 +14477,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>64</v>
@@ -14082,7 +14497,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>64</v>
@@ -14102,7 +14517,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>64</v>
@@ -14122,7 +14537,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>64</v>
@@ -14151,13 +14566,13 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>55</v>
@@ -14180,7 +14595,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>64</v>
@@ -14240,7 +14655,7 @@
         <v>4.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN49" s="3">
         <v>2.0</v>
@@ -14272,7 +14687,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>76</v>
@@ -14292,7 +14707,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>76</v>
@@ -14312,13 +14727,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>60</v>
@@ -14332,13 +14747,13 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>60</v>
@@ -14361,7 +14776,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>76</v>
@@ -14390,13 +14805,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>55</v>
@@ -14419,7 +14834,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>76</v>
@@ -14479,7 +14894,7 @@
         <v>4.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AN56" s="3">
         <v>3.0</v>
@@ -14511,7 +14926,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>85</v>
@@ -14531,7 +14946,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>85</v>
@@ -14551,7 +14966,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>85</v>
@@ -14574,13 +14989,13 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>71</v>
@@ -14603,7 +15018,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>85</v>
@@ -14669,7 +15084,7 @@
         <v>6.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -14701,7 +15116,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>92</v>
@@ -14721,7 +15136,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>92</v>
@@ -14741,7 +15156,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>92</v>
@@ -14764,13 +15179,13 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>71</v>
@@ -14793,7 +15208,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>92</v>
@@ -14822,7 +15237,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>92</v>
@@ -14882,7 +15297,7 @@
         <v>14.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="AN67" s="3">
         <v>2.0</v>
@@ -14914,7 +15329,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>96</v>
@@ -14934,7 +15349,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>96</v>
@@ -14957,7 +15372,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>96</v>
@@ -14986,7 +15401,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>96</v>
@@ -15015,13 +15430,13 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>96</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>55</v>
@@ -15038,7 +15453,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>96</v>
@@ -15101,7 +15516,7 @@
         <v>2.0</v>
       </c>
       <c r="AM73" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AN73" s="3">
         <v>2.0</v>
@@ -15133,7 +15548,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>103</v>
@@ -15153,7 +15568,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>103</v>
@@ -15173,7 +15588,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>103</v>
@@ -15196,7 +15611,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>103</v>
@@ -15225,7 +15640,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>103</v>
@@ -15254,7 +15669,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>103</v>
@@ -15314,7 +15729,7 @@
         <v>7.0</v>
       </c>
       <c r="AM79" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AN79" s="3">
         <v>2.0</v>
@@ -15346,7 +15761,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>49</v>
@@ -15366,7 +15781,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>49</v>
@@ -15386,7 +15801,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>49</v>
@@ -15406,7 +15821,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>49</v>
@@ -15435,7 +15850,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>49</v>
@@ -15464,13 +15879,13 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H85" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>71</v>
@@ -15493,7 +15908,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
@@ -15522,7 +15937,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -15585,7 +16000,7 @@
         <v>3.0</v>
       </c>
       <c r="AM87" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="AN87" s="3">
         <v>4.0</v>
@@ -15617,7 +16032,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>64</v>
@@ -15637,7 +16052,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>64</v>
@@ -15657,7 +16072,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>64</v>
@@ -15677,7 +16092,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>64</v>
@@ -15697,7 +16112,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>64</v>
@@ -15712,7 +16127,7 @@
         <v>100</v>
       </c>
       <c r="L92" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M92" s="3">
         <v>15.0</v>
@@ -15726,7 +16141,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>64</v>
@@ -15755,13 +16170,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H94" s="1" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>71</v>
@@ -15784,7 +16199,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>64</v>
@@ -15844,7 +16259,7 @@
         <v>1.0</v>
       </c>
       <c r="AM95" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AN95" s="3">
         <v>3.0</v>
@@ -15876,7 +16291,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>76</v>
@@ -15896,7 +16311,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>76</v>
@@ -15916,7 +16331,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
@@ -15945,7 +16360,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -15974,7 +16389,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -16037,7 +16452,7 @@
         <v>3.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AN100" s="3">
         <v>2.0</v>
@@ -16069,7 +16484,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>85</v>
@@ -16089,7 +16504,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>85</v>
@@ -16109,7 +16524,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>85</v>
@@ -16129,7 +16544,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>85</v>
@@ -16152,7 +16567,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>85</v>
@@ -16181,7 +16596,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>85</v>
@@ -16247,7 +16662,7 @@
         <v>0.0</v>
       </c>
       <c r="AM106" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN106" s="3">
         <v>1.0</v>
@@ -16279,7 +16694,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>92</v>
@@ -16299,7 +16714,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>92</v>
@@ -16319,7 +16734,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>92</v>
@@ -16339,7 +16754,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>92</v>
@@ -16359,7 +16774,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>92</v>
@@ -16382,7 +16797,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>92</v>
@@ -16411,7 +16826,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>92</v>
@@ -16477,7 +16892,7 @@
         <v>0.0</v>
       </c>
       <c r="AM113" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AN113" s="3">
         <v>1.0</v>
@@ -16509,7 +16924,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>96</v>
@@ -16529,7 +16944,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>96</v>
@@ -16549,7 +16964,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>96</v>
@@ -16569,7 +16984,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>96</v>
@@ -16592,7 +17007,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>96</v>
@@ -16621,7 +17036,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>96</v>
@@ -16650,7 +17065,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>96</v>
@@ -16710,7 +17125,7 @@
         <v>4.0</v>
       </c>
       <c r="AM120" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AN120" s="3">
         <v>2.0</v>
@@ -16742,7 +17157,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>103</v>
@@ -16762,7 +17177,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>103</v>
@@ -16782,7 +17197,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>103</v>
@@ -16802,7 +17217,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>103</v>
@@ -16825,7 +17240,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>103</v>
@@ -16854,7 +17269,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>103</v>
@@ -16920,7 +17335,7 @@
         <v>9.0</v>
       </c>
       <c r="AM126" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="AN126" s="3">
         <v>1.0</v>
@@ -16952,7 +17367,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>49</v>
@@ -16972,7 +17387,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>49</v>
@@ -16992,7 +17407,7 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -17012,7 +17427,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
@@ -17035,7 +17450,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
@@ -17064,7 +17479,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>49</v>
@@ -17093,7 +17508,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>49</v>
@@ -17122,7 +17537,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>49</v>
@@ -17182,7 +17597,7 @@
         <v>4.0</v>
       </c>
       <c r="AM134" s="1" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="AN134" s="3">
         <v>3.0</v>
@@ -17214,7 +17629,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>64</v>
@@ -17234,7 +17649,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>64</v>
@@ -17254,7 +17669,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>64</v>
@@ -17274,7 +17689,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>64</v>
@@ -17294,7 +17709,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>64</v>
@@ -17323,7 +17738,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>64</v>
@@ -17352,7 +17767,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>64</v>
@@ -17415,7 +17830,7 @@
         <v>5.0</v>
       </c>
       <c r="AM141" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AN141" s="3">
         <v>2.0</v>
@@ -17447,7 +17862,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>76</v>
@@ -17467,7 +17882,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>76</v>
@@ -17487,7 +17902,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>76</v>
@@ -17516,13 +17931,13 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>60</v>
@@ -17545,13 +17960,13 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H146" s="1" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="I146" s="2" t="s">
         <v>55</v>
@@ -17568,7 +17983,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>76</v>
@@ -17631,7 +18046,7 @@
         <v>5.0</v>
       </c>
       <c r="AM147" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="AN147" s="3">
         <v>2.0</v>
@@ -17663,7 +18078,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>85</v>
@@ -17683,7 +18098,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>85</v>
@@ -17703,7 +18118,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>85</v>
@@ -17723,7 +18138,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>85</v>
@@ -17746,7 +18161,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>85</v>
@@ -17775,7 +18190,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>85</v>
@@ -17835,7 +18250,7 @@
         <v>1.0</v>
       </c>
       <c r="AM153" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="AN153" s="3">
         <v>1.0</v>
@@ -17867,7 +18282,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>92</v>
@@ -17887,7 +18302,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>92</v>
@@ -17907,7 +18322,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>92</v>
@@ -17930,7 +18345,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>92</v>
@@ -17959,7 +18374,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>92</v>
@@ -17988,7 +18403,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>92</v>
@@ -18051,7 +18466,7 @@
         <v>5.0</v>
       </c>
       <c r="AM159" s="1" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="AN159" s="3">
         <v>2.0</v>
@@ -18083,7 +18498,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>96</v>
@@ -18103,7 +18518,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>96</v>
@@ -18123,7 +18538,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>96</v>
@@ -18146,7 +18561,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>96</v>
@@ -18175,7 +18590,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>96</v>
@@ -18204,7 +18619,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>96</v>
@@ -18267,7 +18682,7 @@
         <v>5.0</v>
       </c>
       <c r="AM165" s="1" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AN165" s="3">
         <v>2.0</v>
@@ -18299,7 +18714,7 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>103</v>
@@ -18319,7 +18734,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>103</v>
@@ -18339,7 +18754,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>103</v>
@@ -18359,7 +18774,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>103</v>
@@ -18382,7 +18797,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>103</v>
@@ -18411,13 +18826,13 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H171" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I171" s="2" t="s">
         <v>55</v>
@@ -18440,7 +18855,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>103</v>
@@ -18503,7 +18918,7 @@
         <v>2.0</v>
       </c>
       <c r="AM172" s="1" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AN172" s="3">
         <v>2.0</v>
@@ -18535,7 +18950,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>49</v>
@@ -18547,7 +18962,7 @@
         <v>51</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G173" s="2" t="s">
         <v>105</v>
@@ -18555,7 +18970,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -18575,7 +18990,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>49</v>
@@ -18595,7 +19010,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>49</v>
@@ -18624,7 +19039,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>49</v>
@@ -18653,7 +19068,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>49</v>
@@ -18682,7 +19097,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>49</v>
@@ -18711,7 +19126,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>49</v>
@@ -18774,7 +19189,7 @@
         <v>10.0</v>
       </c>
       <c r="AM180" s="1" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AN180" s="3">
         <v>4.0</v>
@@ -18806,7 +19221,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>64</v>
@@ -18826,7 +19241,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>64</v>
@@ -18846,7 +19261,7 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>64</v>
@@ -18866,7 +19281,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>64</v>
@@ -18889,7 +19304,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>64</v>
@@ -18918,7 +19333,7 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>64</v>
@@ -18927,7 +19342,7 @@
         <v>88</v>
       </c>
       <c r="I186" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>68</v>
@@ -18947,13 +19362,13 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H187" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I187" s="2" t="s">
         <v>71</v>
@@ -18976,7 +19391,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>64</v>
@@ -19036,7 +19451,7 @@
         <v>7.0</v>
       </c>
       <c r="AM188" s="1" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="AN188" s="3">
         <v>3.0</v>
@@ -19068,7 +19483,7 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>76</v>
@@ -19080,7 +19495,7 @@
         <v>51</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G189" s="2" t="s">
         <v>105</v>
@@ -19088,7 +19503,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>76</v>
@@ -19108,7 +19523,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>76</v>
@@ -19117,7 +19532,7 @@
         <v>50</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E191" s="2" t="s">
         <v>104</v>
@@ -19128,7 +19543,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>76</v>
@@ -19157,13 +19572,13 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H193" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I193" s="2" t="s">
         <v>60</v>
@@ -19180,7 +19595,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>76</v>
@@ -19209,7 +19624,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>76</v>
@@ -19269,7 +19684,7 @@
         <v>0.0</v>
       </c>
       <c r="AM195" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AN195" s="3">
         <v>2.0</v>
@@ -19301,7 +19716,7 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>85</v>
@@ -19321,7 +19736,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>85</v>
@@ -19341,7 +19756,7 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>85</v>
@@ -19361,7 +19776,7 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>85</v>
@@ -19384,7 +19799,7 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>85</v>
@@ -19413,7 +19828,7 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>85</v>
@@ -19476,7 +19891,7 @@
         <v>1.0</v>
       </c>
       <c r="AM201" s="1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="AN201" s="3">
         <v>1.0</v>
@@ -19508,7 +19923,7 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>92</v>
@@ -19528,7 +19943,7 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>92</v>
@@ -19548,7 +19963,7 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>92</v>
@@ -19568,7 +19983,7 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>92</v>
@@ -19591,7 +20006,7 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>92</v>
@@ -19603,7 +20018,7 @@
         <v>55</v>
       </c>
       <c r="L206" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M206" s="3">
         <v>6.0</v>
@@ -19617,19 +20032,19 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H207" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="I207" s="2" t="s">
         <v>71</v>
       </c>
       <c r="L207" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="M207" s="3">
         <v>10.0</v>
@@ -19643,7 +20058,7 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>92</v>
@@ -19893,7 +20308,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>76</v>
@@ -19913,7 +20328,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>76</v>
@@ -19933,13 +20348,13 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>55</v>
@@ -19953,7 +20368,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>76</v>
@@ -19973,7 +20388,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>76</v>
@@ -20002,7 +20417,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>76</v>
@@ -20031,13 +20446,13 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>55</v>
@@ -20054,7 +20469,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>76</v>
@@ -20117,7 +20532,7 @@
         <v>1.0</v>
       </c>
       <c r="AM9" s="1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AN9" s="3">
         <v>2.0</v>
@@ -20149,7 +20564,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>85</v>
@@ -20169,7 +20584,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>85</v>
@@ -20189,7 +20604,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>85</v>
@@ -20212,7 +20627,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>85</v>
@@ -20241,7 +20656,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>85</v>
@@ -20298,7 +20713,7 @@
         <v>0.0</v>
       </c>
       <c r="AM14" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="AN14" s="3">
         <v>1.0</v>
@@ -20330,7 +20745,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>92</v>
@@ -20350,7 +20765,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>92</v>
@@ -20370,7 +20785,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>92</v>
@@ -20390,7 +20805,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>92</v>
@@ -20413,7 +20828,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>92</v>
@@ -20442,13 +20857,13 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>71</v>
@@ -20465,7 +20880,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>92</v>
@@ -20525,7 +20940,7 @@
         <v>4.0</v>
       </c>
       <c r="AM21" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="AN21" s="3">
         <v>1.0</v>
@@ -20557,13 +20972,13 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>51</v>
@@ -20577,7 +20992,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>96</v>
@@ -20597,7 +21012,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>96</v>
@@ -20617,7 +21032,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>96</v>
@@ -20640,7 +21055,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>96</v>
@@ -20669,7 +21084,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>96</v>
@@ -20698,7 +21113,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>96</v>
@@ -20707,7 +21122,7 @@
         <v>1.0</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R28" s="1" t="s">
         <v>58</v>
@@ -20761,7 +21176,7 @@
         <v>2.0</v>
       </c>
       <c r="AM28" s="1" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="AN28" s="3">
         <v>2.0</v>
@@ -20793,13 +21208,13 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>51</v>
@@ -20813,7 +21228,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>103</v>
@@ -20833,7 +21248,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>103</v>
@@ -20853,7 +21268,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>103</v>
@@ -20882,13 +21297,13 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>55</v>
@@ -20911,7 +21326,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>103</v>
@@ -20920,7 +21335,7 @@
         <v>1.0</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R34" s="1" t="s">
         <v>58</v>
@@ -20977,7 +21392,7 @@
         <v>4.0</v>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="AN34" s="3">
         <v>2.0</v>
@@ -21009,7 +21424,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>49</v>
@@ -21029,7 +21444,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>49</v>
@@ -21049,16 +21464,16 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>128</v>
@@ -21069,7 +21484,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>49</v>
@@ -21089,7 +21504,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>49</v>
@@ -21118,7 +21533,7 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>49</v>
@@ -21147,7 +21562,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>49</v>
@@ -21213,7 +21628,7 @@
         <v>12.0</v>
       </c>
       <c r="AM41" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AN41" s="3">
         <v>2.0</v>
@@ -21245,7 +21660,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>64</v>
@@ -21265,7 +21680,7 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>64</v>
@@ -21285,7 +21700,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>64</v>
@@ -21305,7 +21720,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>64</v>
@@ -21325,7 +21740,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>64</v>
@@ -21354,13 +21769,13 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>55</v>
@@ -21383,7 +21798,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>64</v>
@@ -21412,7 +21827,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>64</v>
@@ -21475,7 +21890,7 @@
         <v>7.0</v>
       </c>
       <c r="AM49" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="AN49" s="3">
         <v>3.0</v>
@@ -21507,7 +21922,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>76</v>
@@ -21527,7 +21942,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>76</v>
@@ -21547,7 +21962,7 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>76</v>
@@ -21567,7 +21982,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>76</v>
@@ -21596,13 +22011,13 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I54" s="2" t="s">
         <v>55</v>
@@ -21616,7 +22031,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>76</v>
@@ -21676,7 +22091,7 @@
         <v>1.0</v>
       </c>
       <c r="AM55" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AN55" s="3">
         <v>1.0</v>
@@ -21708,7 +22123,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>85</v>
@@ -21728,7 +22143,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>85</v>
@@ -21748,7 +22163,7 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>85</v>
@@ -21768,7 +22183,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>85</v>
@@ -21791,7 +22206,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>85</v>
@@ -21820,7 +22235,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>85</v>
@@ -21883,7 +22298,7 @@
         <v>2.0</v>
       </c>
       <c r="AM61" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN61" s="3">
         <v>1.0</v>
@@ -21915,7 +22330,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>92</v>
@@ -21935,7 +22350,7 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>92</v>
@@ -21955,7 +22370,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>92</v>
@@ -21978,7 +22393,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>92</v>
@@ -22007,7 +22422,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>92</v>
@@ -22036,7 +22451,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>92</v>
@@ -22099,7 +22514,7 @@
         <v>0.0</v>
       </c>
       <c r="AM67" s="1" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="AN67" s="3">
         <v>2.0</v>
@@ -22131,7 +22546,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>96</v>
@@ -22151,7 +22566,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>96</v>
@@ -22171,7 +22586,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>96</v>
@@ -22191,7 +22606,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>96</v>
@@ -22214,7 +22629,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>96</v>
@@ -22243,7 +22658,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>96</v>
@@ -22272,7 +22687,7 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>96</v>
@@ -22335,7 +22750,7 @@
         <v>3.0</v>
       </c>
       <c r="AM74" s="1" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="AN74" s="3">
         <v>2.0</v>
@@ -22367,7 +22782,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>103</v>
@@ -22387,7 +22802,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>103</v>
@@ -22407,13 +22822,13 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>71</v>
@@ -22427,7 +22842,7 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>103</v>
@@ -22450,7 +22865,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>103</v>
@@ -22479,7 +22894,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>103</v>
@@ -22577,7 +22992,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>49</v>
@@ -22597,7 +23012,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>49</v>
@@ -22617,7 +23032,7 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>49</v>
@@ -22640,7 +23055,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>49</v>
@@ -22669,7 +23084,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>49</v>
@@ -22698,13 +23113,13 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H86" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>55</v>
@@ -22727,7 +23142,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>49</v>
@@ -22793,7 +23208,7 @@
         <v>8.0</v>
       </c>
       <c r="AM87" s="1" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="AN87" s="3">
         <v>3.0</v>
@@ -22825,7 +23240,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>64</v>
@@ -22845,7 +23260,7 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>64</v>
@@ -22865,7 +23280,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>64</v>
@@ -22885,7 +23300,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>64</v>
@@ -22905,7 +23320,7 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>64</v>
@@ -22934,13 +23349,13 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H93" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>71</v>
@@ -22963,7 +23378,7 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>64</v>
@@ -23026,7 +23441,7 @@
         <v>1.0</v>
       </c>
       <c r="AM94" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="AN94" s="3">
         <v>2.0</v>
@@ -23058,7 +23473,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>76</v>
@@ -23078,7 +23493,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>76</v>
@@ -23098,7 +23513,7 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>76</v>
@@ -23127,13 +23542,13 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H98" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>60</v>
@@ -23156,7 +23571,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>76</v>
@@ -23185,7 +23600,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>76</v>
@@ -23245,7 +23660,7 @@
         <v>1.0</v>
       </c>
       <c r="AM100" s="1" t="s">
-        <v>294</v>
+        <v>144</v>
       </c>
       <c r="AN100" s="3">
         <v>3.0</v>
@@ -23277,7 +23692,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>85</v>
@@ -23297,7 +23712,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>85</v>
@@ -23317,7 +23732,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>85</v>
@@ -23340,7 +23755,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>85</v>
@@ -23369,7 +23784,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>85</v>
@@ -23435,7 +23850,7 @@
         <v>3.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="AN105" s="3">
         <v>1.0</v>
@@ -23467,7 +23882,7 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>92</v>
@@ -23487,7 +23902,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>92</v>
@@ -23507,7 +23922,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>92</v>
@@ -23530,13 +23945,13 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H109" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I109" s="2" t="s">
         <v>71</v>
@@ -23559,7 +23974,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>92</v>
@@ -23588,7 +24003,7 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>92</v>
@@ -23657,7 +24072,7 @@
         <v>2.0</v>
       </c>
       <c r="AM111" s="1" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN111" s="3">
         <v>2.0</v>
@@ -23689,7 +24104,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>96</v>
@@ -23709,7 +24124,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>96</v>
@@ -23729,7 +24144,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>96</v>
@@ -23752,7 +24167,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>96</v>
@@ -23781,7 +24196,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>96</v>
@@ -23810,7 +24225,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>96</v>
@@ -23870,7 +24285,7 @@
         <v>3.0</v>
       </c>
       <c r="AM117" s="1" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AN117" s="3">
         <v>2.0</v>
@@ -23902,7 +24317,7 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>103</v>
@@ -23922,7 +24337,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>103</v>
@@ -23942,7 +24357,7 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>103</v>
@@ -23962,7 +24377,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>103</v>
@@ -23985,7 +24400,7 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>103</v>
@@ -24014,7 +24429,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>103</v>
@@ -24043,7 +24458,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>103</v>
@@ -24109,7 +24524,7 @@
         <v>3.0</v>
       </c>
       <c r="AM124" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AN124" s="3">
         <v>2.0</v>
@@ -24141,7 +24556,7 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>49</v>
@@ -24161,7 +24576,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>49</v>
@@ -24181,7 +24596,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>49</v>
@@ -24201,27 +24616,27 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>71</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>49</v>
@@ -24250,7 +24665,7 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>49</v>
@@ -24279,13 +24694,13 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H131" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I131" s="2" t="s">
         <v>55</v>
@@ -24308,7 +24723,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>49</v>
@@ -24337,7 +24752,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>49</v>
@@ -24397,7 +24812,7 @@
         <v>7.0</v>
       </c>
       <c r="AM133" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AN133" s="3">
         <v>4.0</v>
@@ -24429,7 +24844,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>64</v>
@@ -24449,7 +24864,7 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>64</v>
@@ -24469,7 +24884,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>64</v>
@@ -24492,7 +24907,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>64</v>
@@ -24521,7 +24936,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>64</v>
@@ -24550,7 +24965,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>64</v>
@@ -24579,7 +24994,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>64</v>
@@ -24674,7 +25089,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>76</v>
@@ -24694,7 +25109,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>76</v>
@@ -24714,7 +25129,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>76</v>
@@ -24743,13 +25158,13 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H144" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I144" s="2" t="s">
         <v>60</v>
@@ -24766,7 +25181,7 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>76</v>
@@ -24826,7 +25241,7 @@
         <v>2.0</v>
       </c>
       <c r="AM145" s="1" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AN145" s="3">
         <v>1.0</v>
@@ -24858,7 +25273,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>85</v>
@@ -24878,7 +25293,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>85</v>
@@ -24901,13 +25316,13 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H148" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I148" s="2" t="s">
         <v>71</v>
@@ -24930,7 +25345,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>85</v>
@@ -24959,7 +25374,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>85</v>
@@ -25019,7 +25434,7 @@
         <v>1.0</v>
       </c>
       <c r="AM150" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="AN150" s="3">
         <v>2.0</v>
@@ -25051,7 +25466,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>92</v>
@@ -25071,7 +25486,7 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>92</v>
@@ -25094,13 +25509,13 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H153" s="1" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="I153" s="2" t="s">
         <v>55</v>
@@ -25114,7 +25529,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>92</v>
@@ -25143,7 +25558,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>92</v>
@@ -25206,7 +25621,7 @@
         <v>1.0</v>
       </c>
       <c r="AM155" s="1" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="AN155" s="3">
         <v>1.0</v>
@@ -25238,7 +25653,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>96</v>
@@ -25258,7 +25673,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>96</v>
@@ -25278,7 +25693,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>96</v>
@@ -25301,7 +25716,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>96</v>
@@ -25330,7 +25745,7 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>96</v>
@@ -25359,7 +25774,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>96</v>
@@ -25419,7 +25834,7 @@
         <v>5.0</v>
       </c>
       <c r="AM161" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="AN161" s="3">
         <v>2.0</v>
@@ -25451,7 +25866,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>103</v>
@@ -25471,7 +25886,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>103</v>
@@ -25491,7 +25906,7 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>103</v>
@@ -25511,7 +25926,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>103</v>
@@ -25534,13 +25949,13 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H166" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I166" s="2" t="s">
         <v>55</v>
@@ -25563,7 +25978,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>103</v>
@@ -25592,7 +26007,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>103</v>
@@ -25658,7 +26073,7 @@
         <v>0.0</v>
       </c>
       <c r="AM168" s="1" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AN168" s="3">
         <v>2.0</v>
@@ -25690,7 +26105,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>49</v>
@@ -25710,7 +26125,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>49</v>
@@ -25730,7 +26145,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>49</v>
@@ -25750,7 +26165,7 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>49</v>
@@ -25773,7 +26188,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>49</v>
@@ -25802,7 +26217,7 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -25831,7 +26246,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>49</v>
@@ -25891,7 +26306,7 @@
         <v>1.0</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AN175" s="3">
         <v>2.0</v>
@@ -25923,7 +26338,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>64</v>
@@ -25943,7 +26358,7 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>64</v>
@@ -25963,7 +26378,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>64</v>
@@ -25992,13 +26407,13 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H179" s="1" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="I179" s="2" t="s">
         <v>60</v>
@@ -26021,7 +26436,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>64</v>
@@ -26050,13 +26465,13 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H181" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I181" s="2" t="s">
         <v>55</v>
@@ -26073,7 +26488,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>64</v>
@@ -26139,7 +26554,7 @@
         <v>3.0</v>
       </c>
       <c r="AM182" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="AN182" s="3">
         <v>3.0</v>
@@ -26329,7 +26744,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>103</v>
@@ -26349,7 +26764,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>103</v>
@@ -26369,7 +26784,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>103</v>
@@ -26389,13 +26804,13 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>55</v>
@@ -26409,7 +26824,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>103</v>
@@ -26438,7 +26853,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>103</v>
@@ -26467,7 +26882,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>103</v>
@@ -26479,7 +26894,7 @@
         <v>132</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="S8" s="3">
         <v>30436.0</v>
@@ -26533,7 +26948,7 @@
         <v>0.0</v>
       </c>
       <c r="AM8" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AN8" s="3">
         <v>2.0</v>
@@ -26565,7 +26980,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>49</v>
@@ -26585,7 +27000,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>49</v>
@@ -26605,7 +27020,7 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -26625,7 +27040,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>49</v>
@@ -26654,13 +27069,13 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>77</v>
@@ -26677,7 +27092,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>49</v>
@@ -26706,7 +27121,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>49</v>
@@ -26735,7 +27150,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>49</v>
@@ -26795,7 +27210,7 @@
         <v>1.0</v>
       </c>
       <c r="AM16" s="1" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="AN16" s="3">
         <v>3.0</v>
@@ -26827,7 +27242,7 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>64</v>
@@ -26847,7 +27262,7 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>64</v>
@@ -26867,7 +27282,7 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>64</v>
@@ -26890,7 +27305,7 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>64</v>
@@ -26919,7 +27334,7 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>64</v>
@@ -26948,7 +27363,7 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>64</v>
@@ -26977,7 +27392,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>64</v>
@@ -27037,7 +27452,7 @@
         <v>2.0</v>
       </c>
       <c r="AM23" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AN23" s="3">
         <v>3.0</v>
@@ -27069,7 +27484,7 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>76</v>
@@ -27089,7 +27504,7 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>76</v>
@@ -27109,7 +27524,7 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>76</v>
@@ -27129,7 +27544,7 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>76</v>
@@ -27158,7 +27573,7 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>76</v>
@@ -27187,7 +27602,7 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>76</v>
@@ -27247,7 +27662,7 @@
         <v>2.0</v>
       </c>
       <c r="AM29" s="1" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AN29" s="3">
         <v>2.0</v>
@@ -27279,7 +27694,7 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>85</v>
@@ -27299,7 +27714,7 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>85</v>
@@ -27319,7 +27734,7 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>85</v>
@@ -27339,7 +27754,7 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>85</v>
@@ -27362,7 +27777,7 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>85</v>
@@ -27391,7 +27806,7 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>85</v>
@@ -27454,7 +27869,7 @@
         <v>2.0</v>
       </c>
       <c r="AM35" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="AN35" s="3">
         <v>1.0</v>
@@ -27486,7 +27901,7 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>92</v>
@@ -27506,7 +27921,7 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>92</v>
@@ -27518,7 +27933,7 @@
         <v>51</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>105</v>
@@ -27526,7 +27941,7 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>92</v>
@@ -27546,7 +27961,7 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>92</v>
@@ -27575,13 +27990,13 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>55</v>
@@ -27598,7 +28013,7 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>92</v>
@@ -27627,7 +28042,7 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>92</v>
@@ -27719,13 +28134,13 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>51</v>
@@ -27739,7 +28154,7 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>96</v>
@@ -27759,7 +28174,7 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>96</v>
@@ -27779,7 +28194,7 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>96</v>
@@ -27799,7 +28214,7 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>96</v>
@@ -27822,7 +28237,7 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>96</v>
@@ -27851,7 +28266,7 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>96</v>
@@ -27880,7 +28295,7 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>96</v>
@@ -27889,7 +28304,7 @@
         <v>0.0</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R50" s="1" t="s">
         <v>132</v>
@@ -27943,7 +28358,7 @@
         <v>2.0</v>
       </c>
       <c r="AM50" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AN50" s="3">
         <v>2.0</v>
@@ -27975,7 +28390,7 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>103</v>
@@ -27995,13 +28410,13 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>51</v>
@@ -28015,7 +28430,7 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>103</v>
@@ -28035,7 +28450,7 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>103</v>
@@ -28064,13 +28479,13 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I55" s="2" t="s">
         <v>55</v>
@@ -28093,7 +28508,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>103</v>
@@ -28156,7 +28571,7 @@
         <v>6.0</v>
       </c>
       <c r="AM56" s="1" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="AN56" s="3">
         <v>2.0</v>
@@ -28188,7 +28603,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>49</v>
@@ -28208,13 +28623,13 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>60</v>
@@ -28228,7 +28643,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>49</v>
@@ -28248,7 +28663,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>49</v>
@@ -28268,13 +28683,13 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>71</v>
@@ -28288,7 +28703,7 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>49</v>
@@ -28317,13 +28732,13 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H63" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>60</v>
@@ -28340,7 +28755,7 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>49</v>
@@ -28349,7 +28764,7 @@
         <v>98</v>
       </c>
       <c r="I64" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>52</v>
@@ -28369,7 +28784,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>49</v>
@@ -28398,7 +28813,7 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -28458,7 +28873,7 @@
         <v>13.0</v>
       </c>
       <c r="AM66" s="1" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AN66" s="3">
         <v>3.0</v>
@@ -28490,7 +28905,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>64</v>
@@ -28510,13 +28925,13 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>51</v>
@@ -28530,7 +28945,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>64</v>
@@ -28550,7 +28965,7 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>64</v>
@@ -28570,7 +28985,7 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>64</v>
@@ -28590,7 +29005,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>64</v>
@@ -28613,7 +29028,7 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>64</v>
@@ -28642,13 +29057,13 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>55</v>
@@ -28671,7 +29086,7 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>64</v>
@@ -28700,7 +29115,7 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>64</v>
@@ -28763,7 +29178,7 @@
         <v>4.0</v>
       </c>
       <c r="AM76" s="1" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AN76" s="3">
         <v>3.0</v>
@@ -28795,7 +29210,7 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>76</v>
@@ -28815,13 +29230,13 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>60</v>
@@ -28835,7 +29250,7 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>76</v>
@@ -28855,7 +29270,7 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>76</v>
@@ -28875,7 +29290,7 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>76</v>
@@ -28898,7 +29313,7 @@
     </row>
     <row r="82">
       <c r="A82" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>76</v>
@@ -28927,13 +29342,13 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H83" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>55</v>
@@ -28956,7 +29371,7 @@
     </row>
     <row r="84">
       <c r="A84" s="2" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>76</v>
@@ -29022,7 +29437,7 @@
         <v>2.0</v>
       </c>
       <c r="AM84" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="AN84" s="3">
         <v>2.0</v>
@@ -29054,7 +29469,7 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>85</v>
@@ -29074,7 +29489,7 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>85</v>
@@ -29094,7 +29509,7 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>85</v>
@@ -29114,7 +29529,7 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>85</v>
@@ -29137,16 +29552,16 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H89" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>52</v>
@@ -29160,7 +29575,7 @@
     </row>
     <row r="90">
       <c r="A90" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>85</v>
@@ -29189,7 +29604,7 @@
     </row>
     <row r="91">
       <c r="A91" s="2" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>85</v>
@@ -29255,7 +29670,7 @@
         <v>3.0</v>
       </c>
       <c r="AM91" s="1" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AN91" s="3">
         <v>1.0</v>
@@ -29287,13 +29702,13 @@
     </row>
     <row r="92">
       <c r="A92" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C92" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>51</v>
@@ -29307,7 +29722,7 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>92</v>
@@ -29327,13 +29742,13 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>92</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>71</v>
@@ -29347,7 +29762,7 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>92</v>
@@ -29367,7 +29782,7 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>92</v>
@@ -29390,13 +29805,13 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H97" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>55</v>
@@ -29413,7 +29828,7 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>92</v>
@@ -29422,7 +29837,7 @@
         <v>0.0</v>
       </c>
       <c r="Q98" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R98" s="1" t="s">
         <v>79</v>
@@ -29482,7 +29897,7 @@
         <v>6.0</v>
       </c>
       <c r="AM98" s="1" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AN98" s="3">
         <v>0.0</v>
@@ -29514,7 +29929,7 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>96</v>
@@ -29534,7 +29949,7 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>96</v>
@@ -29554,7 +29969,7 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>96</v>
@@ -29574,7 +29989,7 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>96</v>
@@ -29597,7 +30012,7 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>96</v>
@@ -29626,7 +30041,7 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>96</v>
@@ -29655,7 +30070,7 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>96</v>
@@ -29718,7 +30133,7 @@
         <v>2.0</v>
       </c>
       <c r="AM105" s="1" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="AN105" s="3">
         <v>2.0</v>
@@ -29750,13 +30165,13 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>51</v>
@@ -29770,7 +30185,7 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>103</v>
@@ -29790,7 +30205,7 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>103</v>
@@ -29810,7 +30225,7 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>103</v>
@@ -29830,7 +30245,7 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>103</v>
@@ -29859,16 +30274,16 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H111" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>68</v>
@@ -29882,7 +30297,7 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>103</v>
@@ -29911,7 +30326,7 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>103</v>
@@ -29920,7 +30335,7 @@
         <v>0.0</v>
       </c>
       <c r="Q113" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R113" s="1" t="s">
         <v>58</v>
@@ -30006,7 +30421,7 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>49</v>
@@ -30026,7 +30441,7 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>49</v>
@@ -30046,7 +30461,7 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>49</v>
@@ -30066,7 +30481,7 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>49</v>
@@ -30086,13 +30501,13 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>55</v>
@@ -30106,7 +30521,7 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>49</v>
@@ -30135,13 +30550,13 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H120" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>55</v>
@@ -30158,7 +30573,7 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>49</v>
@@ -30187,13 +30602,13 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H122" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I122" s="2" t="s">
         <v>55</v>
@@ -30216,7 +30631,7 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>49</v>
@@ -30279,7 +30694,7 @@
         <v>9.0</v>
       </c>
       <c r="AM123" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AN123" s="3">
         <v>3.0</v>
@@ -30311,7 +30726,7 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>64</v>
@@ -30331,13 +30746,13 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>55</v>
@@ -30351,7 +30766,7 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>64</v>
@@ -30371,7 +30786,7 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>64</v>
@@ -30394,7 +30809,7 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>64</v>
@@ -30423,13 +30838,13 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H129" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I129" s="2" t="s">
         <v>55</v>
@@ -30446,13 +30861,13 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H130" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I130" s="2" t="s">
         <v>55</v>
@@ -30475,7 +30890,7 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>64</v>
@@ -30538,7 +30953,7 @@
         <v>0.0</v>
       </c>
       <c r="AM131" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AN131" s="3">
         <v>2.0</v>
@@ -30570,7 +30985,7 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>76</v>
@@ -30590,7 +31005,7 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>76</v>
@@ -30610,7 +31025,7 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>76</v>
@@ -30630,13 +31045,13 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>55</v>
@@ -30650,7 +31065,7 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>76</v>
@@ -30673,7 +31088,7 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>76</v>
@@ -30702,7 +31117,7 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>76</v>
@@ -30731,7 +31146,7 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>76</v>
@@ -30791,7 +31206,7 @@
         <v>3.0</v>
       </c>
       <c r="AM139" s="1" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AN139" s="3">
         <v>2.0</v>
@@ -30823,7 +31238,7 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>85</v>
@@ -30843,7 +31258,7 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>85</v>
@@ -30863,7 +31278,7 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>85</v>
@@ -30883,7 +31298,7 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>85</v>
@@ -30906,7 +31321,7 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>85</v>
@@ -30935,13 +31350,13 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H145" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I145" s="2" t="s">
         <v>71</v>
@@ -30958,7 +31373,7 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>85</v>
@@ -31021,7 +31436,7 @@
         <v>0.0</v>
       </c>
       <c r="AM146" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AN146" s="3">
         <v>1.0</v>
@@ -31053,7 +31468,7 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>92</v>
@@ -31073,7 +31488,7 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>92</v>
@@ -31093,7 +31508,7 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>92</v>
@@ -31113,7 +31528,7 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>92</v>
@@ -31136,7 +31551,7 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>92</v>
@@ -31165,13 +31580,13 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H152" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I152" s="2" t="s">
         <v>71</v>
@@ -31188,7 +31603,7 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>92</v>
@@ -31251,7 +31666,7 @@
         <v>2.0</v>
       </c>
       <c r="AM153" s="1" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="AN153" s="3">
         <v>1.0</v>
@@ -31283,7 +31698,7 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>96</v>
@@ -31303,7 +31718,7 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>96</v>
@@ -31323,7 +31738,7 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>96</v>
@@ -31346,7 +31761,7 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>96</v>
@@ -31355,7 +31770,7 @@
         <v>98</v>
       </c>
       <c r="I157" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>100</v>
@@ -31375,7 +31790,7 @@
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>96</v>
@@ -31404,7 +31819,7 @@
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>96</v>
@@ -31464,7 +31879,7 @@
         <v>3.0</v>
       </c>
       <c r="AM159" s="1" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AN159" s="3">
         <v>2.0</v>
@@ -31496,13 +31911,13 @@
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>51</v>
@@ -31516,7 +31931,7 @@
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>103</v>
@@ -31536,7 +31951,7 @@
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>103</v>
@@ -31556,7 +31971,7 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>103</v>
@@ -31585,13 +32000,13 @@
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>103</v>
       </c>
       <c r="H164" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I164" s="2" t="s">
         <v>55</v>
@@ -31608,7 +32023,7 @@
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>103</v>
@@ -31617,7 +32032,7 @@
         <v>2.0</v>
       </c>
       <c r="Q165" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="S165" s="3">
         <v>11093.0</v>
@@ -31706,13 +32121,13 @@
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>51</v>
@@ -31726,7 +32141,7 @@
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>49</v>
@@ -31746,7 +32161,7 @@
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>49</v>
@@ -31766,7 +32181,7 @@
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>49</v>
@@ -31786,7 +32201,7 @@
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>49</v>
@@ -31806,7 +32221,7 @@
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>49</v>
@@ -31835,13 +32250,13 @@
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H172" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I172" s="2" t="s">
         <v>55</v>
@@ -31864,7 +32279,7 @@
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>49</v>
@@ -31893,13 +32308,13 @@
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H174" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I174" s="2" t="s">
         <v>55</v>
@@ -31916,7 +32331,7 @@
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>49</v>
@@ -31925,7 +32340,7 @@
         <v>4.0</v>
       </c>
       <c r="Q175" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>54</v>
@@ -31982,7 +32397,7 @@
         <v>7.0</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="AN175" s="3">
         <v>3.0</v>
@@ -32014,7 +32429,7 @@
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>64</v>
@@ -32034,13 +32449,13 @@
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>51</v>
@@ -32054,7 +32469,7 @@
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>64</v>
@@ -32074,7 +32489,7 @@
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>64</v>
@@ -32094,7 +32509,7 @@
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>64</v>
@@ -32114,7 +32529,7 @@
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>64</v>
@@ -32143,7 +32558,7 @@
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>64</v>
@@ -32172,13 +32587,13 @@
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H183" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I183" s="2" t="s">
         <v>55</v>
@@ -32195,7 +32610,7 @@
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>64</v>
@@ -32204,7 +32619,7 @@
         <v>0.0</v>
       </c>
       <c r="Q184" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>54</v>
@@ -32258,7 +32673,7 @@
         <v>0.0</v>
       </c>
       <c r="AM184" s="1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AN184" s="3">
         <v>2.0</v>
@@ -32290,7 +32705,7 @@
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>76</v>
@@ -32310,13 +32725,13 @@
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>76</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D186" s="2" t="s">
         <v>51</v>
@@ -32330,7 +32745,7 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>76</v>
@@ -32350,7 +32765,7 @@
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>76</v>
@@ -32379,13 +32794,13 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>76</v>
       </c>
       <c r="H189" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I189" s="2" t="s">
         <v>77</v>
@@ -32402,7 +32817,7 @@
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>76</v>
@@ -32411,7 +32826,7 @@
         <v>1.0</v>
       </c>
       <c r="Q190" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>79</v>
@@ -32494,7 +32909,7 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>85</v>
@@ -32514,7 +32929,7 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>85</v>
@@ -32534,7 +32949,7 @@
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>85</v>
@@ -32554,7 +32969,7 @@
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>85</v>
@@ -32577,7 +32992,7 @@
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>85</v>
@@ -32606,13 +33021,13 @@
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>85</v>
       </c>
       <c r="H196" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I196" s="2" t="s">
         <v>131</v>
@@ -32635,7 +33050,7 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>85</v>
@@ -32695,7 +33110,7 @@
         <v>1.0</v>
       </c>
       <c r="AM197" s="1" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="AN197" s="3">
         <v>2.0</v>
@@ -32727,7 +33142,7 @@
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B198" s="1" t="s">
         <v>92</v>
@@ -32739,7 +33154,7 @@
         <v>51</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>105</v>
@@ -32747,7 +33162,7 @@
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B199" s="1" t="s">
         <v>92</v>
@@ -32767,7 +33182,7 @@
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B200" s="1" t="s">
         <v>92</v>
@@ -32787,7 +33202,7 @@
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B201" s="1" t="s">
         <v>92</v>
@@ -32810,13 +33225,13 @@
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B202" s="1" t="s">
         <v>92</v>
       </c>
       <c r="H202" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I202" s="2" t="s">
         <v>55</v>
@@ -32833,7 +33248,7 @@
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>92</v>
@@ -32862,7 +33277,7 @@
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B204" s="1" t="s">
         <v>92</v>
@@ -32928,7 +33343,7 @@
         <v>2.0</v>
       </c>
       <c r="AM204" s="1" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="AN204" s="3">
         <v>1.0</v>
@@ -32960,13 +33375,13 @@
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B205" s="1" t="s">
         <v>96</v>
       </c>
       <c r="C205" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>51</v>
@@ -32980,7 +33395,7 @@
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B206" s="1" t="s">
         <v>96</v>
@@ -33000,7 +33415,7 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>96</v>
@@ -33020,7 +33435,7 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B208" s="1" t="s">
         <v>96</v>
@@ -33043,7 +33458,7 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B209" s="1" t="s">
         <v>96</v>
@@ -33072,7 +33487,7 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B210" s="1" t="s">
         <v>96</v>
@@ -33101,7 +33516,7 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B211" s="1" t="s">
         <v>96</v>
@@ -33110,7 +33525,7 @@
         <v>0.0</v>
       </c>
       <c r="Q211" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>132</v>
@@ -33164,7 +33579,7 @@
         <v>1.0</v>
       </c>
       <c r="AM211" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="AN211" s="3">
         <v>2.0</v>
@@ -33196,13 +33611,13 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B212" s="1" t="s">
         <v>103</v>
       </c>
       <c r="C212" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>51</v>
@@ -33216,7 +33631,7 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>103</v>
@@ -33236,7 +33651,7 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B214" s="1" t="s">
         <v>103</v>
@@ -33256,7 +33671,7 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B215" s="1" t="s">
         <v>103</v>
@@ -33285,7 +33700,7 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B216" s="1" t="s">
         <v>103</v>
@@ -33314,7 +33729,7 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>103</v>
@@ -33323,7 +33738,7 @@
         <v>2.0</v>
       </c>
       <c r="Q217" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>132</v>
@@ -33374,7 +33789,7 @@
         <v>4.0</v>
       </c>
       <c r="AM217" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AN217" s="3">
         <v>2.0</v>
@@ -33406,7 +33821,7 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B218" s="1" t="s">
         <v>49</v>
@@ -33426,13 +33841,13 @@
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>49</v>
       </c>
       <c r="C219" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>55</v>
@@ -33446,7 +33861,7 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B220" s="1" t="s">
         <v>49</v>
@@ -33466,7 +33881,7 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B221" s="1" t="s">
         <v>49</v>
@@ -33486,7 +33901,7 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B222" s="1" t="s">
         <v>49</v>
@@ -33515,13 +33930,13 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B223" s="1" t="s">
         <v>49</v>
       </c>
       <c r="H223" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I223" s="2" t="s">
         <v>82</v>
@@ -33538,7 +33953,7 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B224" s="1" t="s">
         <v>49</v>
@@ -33567,7 +33982,7 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B225" s="1" t="s">
         <v>49</v>
@@ -33596,7 +34011,7 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B226" s="1" t="s">
         <v>49</v>
@@ -33659,7 +34074,7 @@
         <v>13.0</v>
       </c>
       <c r="AM226" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="AN226" s="3">
         <v>3.0</v>
@@ -33691,7 +34106,7 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B227" s="1" t="s">
         <v>64</v>
@@ -33711,13 +34126,13 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B228" s="1" t="s">
         <v>64</v>
       </c>
       <c r="C228" s="1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D228" s="2" t="s">
         <v>77</v>
@@ -33731,7 +34146,7 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B229" s="1" t="s">
         <v>64</v>
@@ -33751,7 +34166,7 @@
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B230" s="1" t="s">
         <v>64</v>
@@ -33771,7 +34186,7 @@
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B231" s="1" t="s">
         <v>64</v>
@@ -33791,7 +34206,7 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B232" s="1" t="s">
         <v>64</v>
@@ -33814,7 +34229,7 @@
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B233" s="1" t="s">
         <v>64</v>
@@ -33843,13 +34258,13 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B234" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H234" s="1" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="I234" s="2" t="s">
         <v>71</v>
@@ -33866,13 +34281,13 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B235" s="1" t="s">
         <v>64</v>
       </c>
       <c r="H235" s="1" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I235" s="2" t="s">
         <v>55</v>
@@ -33895,7 +34310,7 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B236" s="1" t="s">
         <v>64</v>
@@ -33958,7 +34373,7 @@
         <v>7.0</v>
       </c>
       <c r="AM236" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AN236" s="3">
         <v>2.0</v>
